--- a/CCTV_Master_List.xlsx
+++ b/CCTV_Master_List.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +40,20 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +105,11 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0037474F"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -120,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -153,6 +170,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -519,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P148"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -660,7 +695,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>ame-krian</t>
+          <t>ame-gudang-krian</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -779,7 +814,7 @@
         </is>
       </c>
       <c r="P3" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -1098,10 +1133,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P7" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P7" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1180,10 +1213,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P8" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P8" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1262,10 +1293,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P9" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P9" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1344,10 +1373,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P10" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P10" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1749,18 +1776,52 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>sgi-batulicin</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>192.168.19.170</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>acti_snvr</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1884,10 +1945,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P18" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P18" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2551,7 +2610,7 @@
         </is>
       </c>
       <c r="P28" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -2769,7 +2828,7 @@
         </is>
       </c>
       <c r="P32" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -3055,7 +3114,7 @@
         </is>
       </c>
       <c r="P36" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3260,10 +3319,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P39" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P39" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3434,10 +3491,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P42" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P42" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3826,10 +3881,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P49" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P49" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3865,18 +3918,52 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>sgi-sampit</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>10.70.130.200</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>1234qwer</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>hikvision</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4046,10 +4133,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P53" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P53" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4187,7 +4272,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>192.168.18.200</t>
+          <t>192.168.18.170</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -4212,18 +4297,16 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>hikvision</t>
+          <t>acti_snvr</t>
         </is>
       </c>
       <c r="O56" s="12" t="inlineStr">
         <is>
-          <t>unreachable</t>
-        </is>
-      </c>
-      <c r="P56" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="P56" s="12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -4302,10 +4385,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P57" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P57" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -4636,10 +4717,8 @@
           <t>auth_error</t>
         </is>
       </c>
-      <c r="P62" s="13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P62" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5017,7 +5096,7 @@
         </is>
       </c>
       <c r="P68" s="11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69">
@@ -5096,10 +5175,8 @@
           <t>failed</t>
         </is>
       </c>
-      <c r="P69" s="13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P69" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -5140,7 +5217,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>sig-cikande</t>
+          <t>sgi-cikande</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -5215,18 +5292,52 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr"/>
-      <c r="O71" s="2" t="inlineStr"/>
-      <c r="P71" s="2" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>sig-cikarang-cbc</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>192.168.67.200</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>P4SSW0RD</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>hilook</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5266,7 +5377,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>sig-cilamaya</t>
+          <t>smt-cilamaya</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -5678,7 +5789,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>sig-lampung-tengah</t>
+          <t>sig-lampung-3</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -5922,10 +6033,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P81" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P81" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -6176,10 +6285,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P85" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P85" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -6258,10 +6365,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P86" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P86" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -8184,10 +8289,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P123" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P123" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -8361,7 +8464,7 @@
         </is>
       </c>
       <c r="P126" s="11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127">
@@ -8424,10 +8527,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P127" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P127" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -8910,10 +9011,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P136" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P136" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -9232,10 +9331,8 @@
           <t>auth_error</t>
         </is>
       </c>
-      <c r="P141" s="13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P141" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -9370,7 +9467,7 @@
       <c r="A144" s="5" t="inlineStr"/>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Sig Cikarang Cbc</t>
+          <t>Sig Kendal 1</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr"/>
@@ -9388,12 +9485,12 @@
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>sig-cikarang-cbc</t>
+          <t>sig-kendal-1</t>
         </is>
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>192.168.67.200</t>
+          <t>192.168.2.100</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
@@ -9413,30 +9510,28 @@
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>P4SSW0RD</t>
+          <t>Indogas*19#</t>
         </is>
       </c>
       <c r="N144" s="5" t="inlineStr">
         <is>
-          <t>hilook</t>
-        </is>
-      </c>
-      <c r="O144" s="12" t="inlineStr">
-        <is>
-          <t>unreachable</t>
-        </is>
-      </c>
-      <c r="P144" s="12" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+          <t>hikvision</t>
+        </is>
+      </c>
+      <c r="O144" s="11" t="inlineStr">
+        <is>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="P144" s="11" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr"/>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Sig Kendal 1</t>
+          <t>Sig Rungkut Sier</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr"/>
@@ -9454,12 +9549,12 @@
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>sig-kendal-1</t>
+          <t>sig-rungkut-sier</t>
         </is>
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>192.168.2.100</t>
+          <t>10.70.90.200</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
@@ -9479,12 +9574,12 @@
       </c>
       <c r="M145" s="5" t="inlineStr">
         <is>
-          <t>Indogas*19#</t>
+          <t>123456</t>
         </is>
       </c>
       <c r="N145" s="5" t="inlineStr">
         <is>
-          <t>hikvision</t>
+          <t>acti_snvr</t>
         </is>
       </c>
       <c r="O145" s="11" t="inlineStr">
@@ -9493,14 +9588,14 @@
         </is>
       </c>
       <c r="P145" s="11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr"/>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Sig Rungkut Sier</t>
+          <t>SGI Kediri</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr"/>
@@ -9518,12 +9613,12 @@
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>sig-rungkut-sier</t>
+          <t>sgi-kediri</t>
         </is>
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>10.70.90.200</t>
+          <t>10.70.137.201</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
@@ -9543,20 +9638,20 @@
       </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>Aremania87</t>
         </is>
       </c>
       <c r="N146" s="5" t="inlineStr">
         <is>
-          <t>acti_snvr</t>
-        </is>
-      </c>
-      <c r="O146" s="11" t="inlineStr">
-        <is>
-          <t>synced</t>
-        </is>
-      </c>
-      <c r="P146" s="11" t="n">
+          <t>hikvision</t>
+        </is>
+      </c>
+      <c r="O146" s="12" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
+      <c r="P146" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9564,7 +9659,7 @@
       <c r="A147" s="5" t="inlineStr"/>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Smu Kediri Sgi</t>
+          <t>Smu Sidoarjo Sgi</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr"/>
@@ -9582,12 +9677,12 @@
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>smu-kediri-sgi</t>
+          <t>smu-sidoarjo-sgi</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>10.70.137.201</t>
+          <t>10.70.140.200</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
@@ -9607,12 +9702,12 @@
       </c>
       <c r="M147" s="5" t="inlineStr">
         <is>
-          <t>Aremania87</t>
+          <t>123456</t>
         </is>
       </c>
       <c r="N147" s="5" t="inlineStr">
         <is>
-          <t>hikvision</t>
+          <t>acti_snvr</t>
         </is>
       </c>
       <c r="O147" s="12" t="inlineStr">
@@ -9620,76 +9715,8 @@
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P147" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="5" t="inlineStr"/>
-      <c r="B148" s="5" t="inlineStr">
-        <is>
-          <t>Smu Sidoarjo Sgi</t>
-        </is>
-      </c>
-      <c r="C148" s="5" t="inlineStr"/>
-      <c r="D148" s="5" t="inlineStr"/>
-      <c r="E148" s="5" t="inlineStr"/>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>Not in SHE Request</t>
-        </is>
-      </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="inlineStr">
-        <is>
-          <t>smu-sidoarjo-sgi</t>
-        </is>
-      </c>
-      <c r="I148" s="5" t="inlineStr">
-        <is>
-          <t>10.70.140.200</t>
-        </is>
-      </c>
-      <c r="J148" s="5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K148" s="5" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="L148" s="5" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="M148" s="5" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="N148" s="5" t="inlineStr">
-        <is>
-          <t>acti_snvr</t>
-        </is>
-      </c>
-      <c r="O148" s="12" t="inlineStr">
-        <is>
-          <t>unreachable</t>
-        </is>
-      </c>
-      <c r="P148" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P147" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9704,70 +9731,262 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Meaning</t>
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>ROW COLOR</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>MEANING</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pink / Light Red</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Requested by SHE — site is in the SHE access request list</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>In SHE request list AND in DB (configured)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>In SHE request list but NOT in DB (needs to be added)</t>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Active &amp; synced — NVR is reachable and confirmed in DB</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>In DB but NOT in SHE request list (extra sites)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Pink</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>NVR is unreachable</t>
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>Yellow / Amber</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Not in SHE request — site is in DB but was not requested by SHE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>SYNC STATUS</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>MEANING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>NVR is reachable and device info has been retrieved successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>NVR did not respond within timeout — network/VPN issue or device offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>auth_error</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>NVR responded but login failed — credentials need to be updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>NVR responded but ISAPI returned an error — possibly wrong vendor type</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Not yet probed since last import</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>COLUMN</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>MEANING</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>Plant Code</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Epicor plant code (e.g. SGI046)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Site Name</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Official site name used in SHE/Epicor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Legal entity (SGI, SIG, AME, SMT, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>SHE Status</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Whether SHE has requested CCTV access for this site</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>In DB</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>YES = NVR is registered in the CCTV system database</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>DB Code</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Unique identifier used in the CCTV system (slug format)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>NVR IP</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>IP address of the NVR on the internal network</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>NVR brand/protocol: hikvision | acti_snvr | uniview | hilook</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>Sync Status</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Result of last probe (see Sync Status table above)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Number of camera channels discovered on this NVR</t>
         </is>
       </c>
     </row>

--- a/CCTV_Master_List.xlsx
+++ b/CCTV_Master_List.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="CCTV Master List" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Playback Test" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CCTV Master List'!$A$1:$P$1</definedName>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +53,17 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -110,8 +120,33 @@
         <fgColor rgb="0037474F"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E4057"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF5CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -133,11 +168,17 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -187,6 +228,69 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9993,4 +10097,1370 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Playback Test Results — 2026-06-23, Channel 1, 10:00–10:01 WIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>52 NVRs tested  |  24 Works  |  26 No Recording  |  2 API Not Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Site Code</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>Playback Status</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>arohera-lt3</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>depo-pangkalan-bun</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>depo-purwodadi</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>depo-rembang</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>ho-sby-lantai-15</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>satoe</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>sgi-bandung</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>sgi-batam</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>sgi-batam-2</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>sgi-cikande</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>sgi-cikupa</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>sgi-lubuk-gaung-dumai</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>sgi-rantau-prapat</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>sgi-tebing-tinggi</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>sig-baturaja</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>sig-kendal</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>sig-kendal-1</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>sig-lampung-3</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E21" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>sig-lampung-ultimate</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>sig-medan</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E23" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>sig-medan-plant</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>sig-pulogadung</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>Hilook</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E25" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>sig-subang-pabrikan-pos</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>smt-cilamaya</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="inlineStr">
+        <is>
+          <t>✅ Works</t>
+        </is>
+      </c>
+      <c r="E27" s="29" t="inlineStr">
+        <is>
+          <t>1 segment found</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>sgi-cilegon</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>NVR reachable, no footage at this time</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>sgi-daanmogot</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>NVR reachable, no footage at this time</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>sig-bekasi-cibitung</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="inlineStr">
+        <is>
+          <t>NVR reachable, no footage at this time</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>head-office-jakarta</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D31" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>sandana-adi-prakarsa</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>sandana-baswara-gas</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D33" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>sgi-batakan</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E34" s="32" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>sgi-boyolali</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E35" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>sgi-duri</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D36" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E36" s="32" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>sgi-jambi</t>
+        </is>
+      </c>
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E37" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>sgi-klaten</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D38" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E38" s="32" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>sgi-kudus</t>
+        </is>
+      </c>
+      <c r="C39" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E39" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>sgi-kutai</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E40" s="32" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>sgi-madiun</t>
+        </is>
+      </c>
+      <c r="C41" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E41" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="31" t="inlineStr">
+        <is>
+          <t>sgi-magelang</t>
+        </is>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E42" s="32" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="34" t="inlineStr">
+        <is>
+          <t>sgi-malang</t>
+        </is>
+      </c>
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E43" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="30" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="31" t="inlineStr">
+        <is>
+          <t>sgi-pier</t>
+        </is>
+      </c>
+      <c r="C44" s="31" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D44" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E44" s="32" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>sgi-sibolga</t>
+        </is>
+      </c>
+      <c r="C45" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D45" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E45" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="30" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>sgi-tuban</t>
+        </is>
+      </c>
+      <c r="C46" s="31" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D46" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E46" s="32" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="34" t="inlineStr">
+        <is>
+          <t>sig-bandung</t>
+        </is>
+      </c>
+      <c r="C47" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D47" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E47" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="30" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="31" t="inlineStr">
+        <is>
+          <t>sig-gorontalo</t>
+        </is>
+      </c>
+      <c r="C48" s="31" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E48" s="32" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="34" t="inlineStr">
+        <is>
+          <t>sig-manado</t>
+        </is>
+      </c>
+      <c r="C49" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D49" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E49" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="30" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>sig-pekanbaru</t>
+        </is>
+      </c>
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D50" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E50" s="32" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="34" t="inlineStr">
+        <is>
+          <t>sig-rungkut-sier</t>
+        </is>
+      </c>
+      <c r="C51" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D51" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E51" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="30" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="31" t="inlineStr">
+        <is>
+          <t>sig-siantar</t>
+        </is>
+      </c>
+      <c r="C52" s="31" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D52" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E52" s="32" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="34" t="inlineStr">
+        <is>
+          <t>sig-ternate</t>
+        </is>
+      </c>
+      <c r="C53" s="34" t="inlineStr">
+        <is>
+          <t>ACTi SNVR</t>
+        </is>
+      </c>
+      <c r="D53" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ No Recording Found</t>
+        </is>
+      </c>
+      <c r="E53" s="35" t="inlineStr">
+        <is>
+          <t>ACTi search API works, no footage returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="36" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="37" t="inlineStr">
+        <is>
+          <t>ame-gudang-krian</t>
+        </is>
+      </c>
+      <c r="C54" s="37" t="inlineStr">
+        <is>
+          <t>Uniview</t>
+        </is>
+      </c>
+      <c r="D54" s="37" t="inlineStr">
+        <is>
+          <t>❌ API Not Supported</t>
+        </is>
+      </c>
+      <c r="E54" s="38" t="inlineStr">
+        <is>
+          <t>Missing /ISAPI/ContentMgmt/search — needs Uniview playback impl</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="39" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="40" t="inlineStr">
+        <is>
+          <t>sgi-bangka</t>
+        </is>
+      </c>
+      <c r="C55" s="40" t="inlineStr">
+        <is>
+          <t>Uniview</t>
+        </is>
+      </c>
+      <c r="D55" s="40" t="inlineStr">
+        <is>
+          <t>❌ API Not Supported</t>
+        </is>
+      </c>
+      <c r="E55" s="41" t="inlineStr">
+        <is>
+          <t>Missing /ISAPI/ContentMgmt/search — needs Uniview playback impl</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/CCTV_Master_List.xlsx
+++ b/CCTV_Master_List.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20460" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CCTV Master List" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CCTV Master List'!$A$1:$P$1</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -30,40 +29,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="13"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -72,77 +79,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEBEE"/>
+        <fgColor rgb="FFFFEBEE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
+        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E1"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="FF37474F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0037474F"/>
+        <fgColor rgb="FF2E4057"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FFD9F0D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9F0D9"/>
+        <fgColor rgb="FFFFF5CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF5CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD9D9"/>
+        <fgColor rgb="FFFFD9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -156,29 +158,39 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -195,11 +207,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -209,35 +216,44 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -246,6 +262,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -257,45 +291,19 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -659,27 +667,23 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P147"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" style="35" min="1" max="1"/>
+    <col width="30" customWidth="1" style="35" min="2" max="2"/>
+    <col width="10" customWidth="1" style="35" min="3" max="3"/>
+    <col width="18" customWidth="1" style="35" min="4" max="4"/>
+    <col width="22" customWidth="1" style="35" min="5" max="6"/>
+    <col width="8" customWidth="1" style="35" min="7" max="7"/>
+    <col width="28" customWidth="1" style="35" min="8" max="8"/>
+    <col width="16" customWidth="1" style="35" min="9" max="9"/>
+    <col width="10" customWidth="1" style="35" min="10" max="11"/>
+    <col width="18" customWidth="1" style="35" min="12" max="13"/>
+    <col width="12" customWidth="1" style="35" min="14" max="15"/>
+    <col width="10" customWidth="1" style="35" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" s="35">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Plant Code</t>
@@ -912,12 +916,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P3" s="11" t="n">
+      <c r="P3" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -992,12 +996,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P4" s="11" t="n">
+      <c r="P4" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1072,12 +1076,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P5" s="11" t="n">
+      <c r="P5" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1152,12 +1156,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1232,12 +1236,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O7" s="12" t="inlineStr">
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P7" s="12" t="n">
+      <c r="P7" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1312,12 +1316,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O8" s="12" t="inlineStr">
+      <c r="O8" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P8" s="12" t="n">
+      <c r="P8" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1392,12 +1396,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O9" s="12" t="inlineStr">
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="P9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1472,12 +1476,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="O10" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P10" s="12" t="n">
+      <c r="P10" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1552,12 +1556,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P11" s="11" t="n">
+      <c r="P11" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1632,12 +1636,12 @@
           <t>uniview</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P12" s="11" t="n">
+      <c r="P12" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1677,15 +1681,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1758,12 +1762,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P14" s="11" t="n">
+      <c r="P14" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1838,12 +1842,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P15" s="11" t="n">
+      <c r="P15" s="5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1963,15 +1967,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -2044,12 +2048,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O18" s="12" t="inlineStr">
+      <c r="O18" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P18" s="12" t="n">
+      <c r="P18" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2124,12 +2128,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O19" s="11" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P19" s="11" t="n">
+      <c r="P19" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2169,15 +2173,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -2250,12 +2254,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O21" s="11" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P21" s="11" t="n">
+      <c r="P21" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2295,15 +2299,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -2376,12 +2380,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O23" s="11" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P23" s="11" t="n">
+      <c r="P23" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2421,15 +2425,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -2502,12 +2506,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O25" s="11" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P25" s="11" t="n">
+      <c r="P25" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2582,12 +2586,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O26" s="11" t="inlineStr">
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P26" s="11" t="n">
+      <c r="P26" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2627,15 +2631,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2708,12 +2712,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O28" s="11" t="inlineStr">
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P28" s="11" t="n">
+      <c r="P28" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2753,15 +2757,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2799,15 +2803,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2845,15 +2849,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -2926,12 +2930,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O32" s="11" t="inlineStr">
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P32" s="11" t="n">
+      <c r="P32" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2971,15 +2975,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -3052,12 +3056,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O34" s="11" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P34" s="11" t="n">
+      <c r="P34" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3132,12 +3136,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O35" s="11" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P35" s="11" t="n">
+      <c r="P35" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3212,13 +3216,13 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O36" s="11" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P36" s="11" t="n">
-        <v>7</v>
+      <c r="P36" s="5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -3257,15 +3261,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -3338,12 +3342,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O38" s="11" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P38" s="11" t="n">
+      <c r="P38" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3418,12 +3422,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O39" s="12" t="inlineStr">
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P39" s="12" t="n">
+      <c r="P39" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3463,15 +3467,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3509,15 +3513,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -3590,12 +3594,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O42" s="12" t="inlineStr">
+      <c r="O42" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P42" s="12" t="n">
+      <c r="P42" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3635,15 +3639,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3678,18 +3682,52 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" s="2" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H44" s="37" t="inlineStr">
+        <is>
+          <t>sgi-padang</t>
+        </is>
+      </c>
+      <c r="I44" s="37" t="inlineStr">
+        <is>
+          <t>10.70.219.250</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="L44" s="37" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="M44" s="37" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>hikvision</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3727,15 +3765,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3773,15 +3811,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3819,15 +3857,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
+      <c r="P47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -3900,12 +3938,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O48" s="11" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P48" s="11" t="n">
+      <c r="P48" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3980,12 +4018,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O49" s="12" t="inlineStr">
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P49" s="12" t="n">
+      <c r="P49" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4105,15 +4143,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4151,15 +4189,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -4232,12 +4270,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O53" s="12" t="inlineStr">
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P53" s="12" t="n">
+      <c r="P53" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4277,15 +4315,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4323,15 +4361,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr"/>
-      <c r="O55" s="2" t="inlineStr"/>
-      <c r="P55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -4384,10 +4422,8 @@
           <t>80</t>
         </is>
       </c>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
+      <c r="K56" s="3" t="n">
+        <v>7070</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
@@ -4401,15 +4437,15 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>acti_snvr</t>
-        </is>
-      </c>
-      <c r="O56" s="12" t="inlineStr">
+          <t>acti_d32</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P56" s="12" t="n">
+      <c r="P56" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4484,12 +4520,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O57" s="12" t="inlineStr">
+      <c r="O57" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P57" s="12" t="n">
+      <c r="P57" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4529,15 +4565,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="n"/>
+      <c r="P58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -4610,12 +4646,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O59" s="11" t="inlineStr">
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P59" s="11" t="n">
+      <c r="P59" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4655,15 +4691,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
+      <c r="P60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -4736,12 +4772,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O61" s="11" t="inlineStr">
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P61" s="11" t="n">
+      <c r="P61" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4816,12 +4852,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O62" s="13" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>auth_error</t>
         </is>
       </c>
-      <c r="P62" s="13" t="n">
+      <c r="P62" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4861,15 +4897,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr"/>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="n"/>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="n"/>
+      <c r="P63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4907,15 +4943,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr"/>
-      <c r="P64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n"/>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -4988,12 +5024,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O65" s="11" t="inlineStr">
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P65" s="11" t="n">
+      <c r="P65" s="5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5033,15 +5069,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr"/>
-      <c r="P66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="n"/>
+      <c r="M66" s="2" t="n"/>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -5114,12 +5150,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O67" s="11" t="inlineStr">
+      <c r="O67" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P67" s="11" t="n">
+      <c r="P67" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5194,12 +5230,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O68" s="11" t="inlineStr">
+      <c r="O68" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P68" s="11" t="n">
+      <c r="P68" s="5" t="n">
         <v>31</v>
       </c>
     </row>
@@ -5274,12 +5310,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O69" s="14" t="inlineStr">
+      <c r="O69" s="8" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="P69" s="13" t="n">
+      <c r="P69" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5354,12 +5390,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O70" s="11" t="inlineStr">
+      <c r="O70" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P70" s="11" t="n">
+      <c r="P70" s="5" t="n">
         <v>32</v>
       </c>
     </row>
@@ -5436,7 +5472,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>unreachable</t>
+          <t>synced</t>
         </is>
       </c>
       <c r="P71" s="2" t="n">
@@ -5594,12 +5630,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O73" s="11" t="inlineStr">
+      <c r="O73" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P73" s="11" t="n">
+      <c r="P73" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5674,12 +5710,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O74" s="11" t="inlineStr">
+      <c r="O74" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P74" s="11" t="n">
+      <c r="P74" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5754,12 +5790,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O75" s="11" t="inlineStr">
+      <c r="O75" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P75" s="11" t="n">
+      <c r="P75" s="5" t="n">
         <v>26</v>
       </c>
     </row>
@@ -5799,15 +5835,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="n"/>
+      <c r="K76" s="2" t="n"/>
+      <c r="L76" s="2" t="n"/>
+      <c r="M76" s="2" t="n"/>
+      <c r="N76" s="2" t="n"/>
+      <c r="O76" s="2" t="n"/>
+      <c r="P76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5845,15 +5881,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr"/>
-      <c r="O77" s="2" t="inlineStr"/>
-      <c r="P77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="2" t="n"/>
+      <c r="L77" s="2" t="n"/>
+      <c r="M77" s="2" t="n"/>
+      <c r="N77" s="2" t="n"/>
+      <c r="O77" s="2" t="n"/>
+      <c r="P77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -6006,12 +6042,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O79" s="11" t="inlineStr">
+      <c r="O79" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P79" s="11" t="n">
+      <c r="P79" s="5" t="n">
         <v>16</v>
       </c>
     </row>
@@ -6051,15 +6087,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="n"/>
+      <c r="K80" s="2" t="n"/>
+      <c r="L80" s="2" t="n"/>
+      <c r="M80" s="2" t="n"/>
+      <c r="N80" s="2" t="n"/>
+      <c r="O80" s="2" t="n"/>
+      <c r="P80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -6132,12 +6168,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O81" s="12" t="inlineStr">
+      <c r="O81" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P81" s="12" t="n">
+      <c r="P81" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6177,15 +6213,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr"/>
-      <c r="P82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="2" t="n"/>
+      <c r="K82" s="2" t="n"/>
+      <c r="L82" s="2" t="n"/>
+      <c r="M82" s="2" t="n"/>
+      <c r="N82" s="2" t="n"/>
+      <c r="O82" s="2" t="n"/>
+      <c r="P82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -6258,12 +6294,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O83" s="11" t="inlineStr">
+      <c r="O83" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P83" s="11" t="n">
+      <c r="P83" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6303,15 +6339,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" s="2" t="n"/>
+      <c r="N84" s="2" t="n"/>
+      <c r="O84" s="2" t="n"/>
+      <c r="P84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -6384,12 +6420,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O85" s="12" t="inlineStr">
+      <c r="O85" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P85" s="12" t="n">
+      <c r="P85" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6464,12 +6500,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O86" s="12" t="inlineStr">
+      <c r="O86" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P86" s="12" t="n">
+      <c r="P86" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6544,12 +6580,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O87" s="11" t="inlineStr">
+      <c r="O87" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P87" s="11" t="n">
+      <c r="P87" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6589,15 +6625,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="2" t="n"/>
+      <c r="M88" s="2" t="n"/>
+      <c r="N88" s="2" t="n"/>
+      <c r="O88" s="2" t="n"/>
+      <c r="P88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -6670,12 +6706,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O89" s="11" t="inlineStr">
+      <c r="O89" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P89" s="11" t="n">
+      <c r="P89" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6750,12 +6786,12 @@
           <t>hilook</t>
         </is>
       </c>
-      <c r="O90" s="11" t="inlineStr">
+      <c r="O90" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P90" s="11" t="n">
+      <c r="P90" s="5" t="n">
         <v>23</v>
       </c>
     </row>
@@ -6795,15 +6831,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr"/>
-      <c r="O91" s="2" t="inlineStr"/>
-      <c r="P91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="n"/>
+      <c r="I91" s="2" t="n"/>
+      <c r="J91" s="2" t="n"/>
+      <c r="K91" s="2" t="n"/>
+      <c r="L91" s="2" t="n"/>
+      <c r="M91" s="2" t="n"/>
+      <c r="N91" s="2" t="n"/>
+      <c r="O91" s="2" t="n"/>
+      <c r="P91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6841,15 +6877,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr"/>
-      <c r="P92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="n"/>
+      <c r="I92" s="2" t="n"/>
+      <c r="J92" s="2" t="n"/>
+      <c r="K92" s="2" t="n"/>
+      <c r="L92" s="2" t="n"/>
+      <c r="M92" s="2" t="n"/>
+      <c r="N92" s="2" t="n"/>
+      <c r="O92" s="2" t="n"/>
+      <c r="P92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6887,15 +6923,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr"/>
-      <c r="O93" s="2" t="inlineStr"/>
-      <c r="P93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="n"/>
+      <c r="I93" s="2" t="n"/>
+      <c r="J93" s="2" t="n"/>
+      <c r="K93" s="2" t="n"/>
+      <c r="L93" s="2" t="n"/>
+      <c r="M93" s="2" t="n"/>
+      <c r="N93" s="2" t="n"/>
+      <c r="O93" s="2" t="n"/>
+      <c r="P93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6933,15 +6969,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr"/>
-      <c r="O94" s="2" t="inlineStr"/>
-      <c r="P94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="n"/>
+      <c r="I94" s="2" t="n"/>
+      <c r="J94" s="2" t="n"/>
+      <c r="K94" s="2" t="n"/>
+      <c r="L94" s="2" t="n"/>
+      <c r="M94" s="2" t="n"/>
+      <c r="N94" s="2" t="n"/>
+      <c r="O94" s="2" t="n"/>
+      <c r="P94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -7014,12 +7050,12 @@
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O95" s="11" t="inlineStr">
+      <c r="O95" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P95" s="11" t="n">
+      <c r="P95" s="5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -7056,18 +7092,52 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
-      <c r="O96" s="2" t="inlineStr"/>
-      <c r="P96" s="2" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H96" s="37" t="inlineStr">
+        <is>
+          <t>sgi-tamora</t>
+        </is>
+      </c>
+      <c r="I96" s="37" t="inlineStr">
+        <is>
+          <t>192.168.56.100</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="L96" s="37" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="M96" s="37" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>hikvision</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -7140,12 +7210,12 @@
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O97" s="11" t="inlineStr">
+      <c r="O97" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P97" s="11" t="n">
+      <c r="P97" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7185,15 +7255,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr"/>
-      <c r="P98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="n"/>
+      <c r="I98" s="2" t="n"/>
+      <c r="J98" s="2" t="n"/>
+      <c r="K98" s="2" t="n"/>
+      <c r="L98" s="2" t="n"/>
+      <c r="M98" s="2" t="n"/>
+      <c r="N98" s="2" t="n"/>
+      <c r="O98" s="2" t="n"/>
+      <c r="P98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -7231,15 +7301,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr"/>
-      <c r="O99" s="2" t="inlineStr"/>
-      <c r="P99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="n"/>
+      <c r="I99" s="2" t="n"/>
+      <c r="J99" s="2" t="n"/>
+      <c r="K99" s="2" t="n"/>
+      <c r="L99" s="2" t="n"/>
+      <c r="M99" s="2" t="n"/>
+      <c r="N99" s="2" t="n"/>
+      <c r="O99" s="2" t="n"/>
+      <c r="P99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -7277,15 +7347,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
-      <c r="P100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="n"/>
+      <c r="I100" s="2" t="n"/>
+      <c r="J100" s="2" t="n"/>
+      <c r="K100" s="2" t="n"/>
+      <c r="L100" s="2" t="n"/>
+      <c r="M100" s="2" t="n"/>
+      <c r="N100" s="2" t="n"/>
+      <c r="O100" s="2" t="n"/>
+      <c r="P100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -7323,15 +7393,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr"/>
-      <c r="P101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="n"/>
+      <c r="I101" s="2" t="n"/>
+      <c r="J101" s="2" t="n"/>
+      <c r="K101" s="2" t="n"/>
+      <c r="L101" s="2" t="n"/>
+      <c r="M101" s="2" t="n"/>
+      <c r="N101" s="2" t="n"/>
+      <c r="O101" s="2" t="n"/>
+      <c r="P101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7369,15 +7439,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
-      <c r="P102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="n"/>
+      <c r="I102" s="2" t="n"/>
+      <c r="J102" s="2" t="n"/>
+      <c r="K102" s="2" t="n"/>
+      <c r="L102" s="2" t="n"/>
+      <c r="M102" s="2" t="n"/>
+      <c r="N102" s="2" t="n"/>
+      <c r="O102" s="2" t="n"/>
+      <c r="P102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -7415,15 +7485,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
-      <c r="P103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="n"/>
+      <c r="I103" s="2" t="n"/>
+      <c r="J103" s="2" t="n"/>
+      <c r="K103" s="2" t="n"/>
+      <c r="L103" s="2" t="n"/>
+      <c r="M103" s="2" t="n"/>
+      <c r="N103" s="2" t="n"/>
+      <c r="O103" s="2" t="n"/>
+      <c r="P103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -7461,15 +7531,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr"/>
-      <c r="P104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="n"/>
+      <c r="I104" s="2" t="n"/>
+      <c r="J104" s="2" t="n"/>
+      <c r="K104" s="2" t="n"/>
+      <c r="L104" s="2" t="n"/>
+      <c r="M104" s="2" t="n"/>
+      <c r="N104" s="2" t="n"/>
+      <c r="O104" s="2" t="n"/>
+      <c r="P104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7507,15 +7577,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr"/>
-      <c r="O105" s="2" t="inlineStr"/>
-      <c r="P105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="n"/>
+      <c r="I105" s="2" t="n"/>
+      <c r="J105" s="2" t="n"/>
+      <c r="K105" s="2" t="n"/>
+      <c r="L105" s="2" t="n"/>
+      <c r="M105" s="2" t="n"/>
+      <c r="N105" s="2" t="n"/>
+      <c r="O105" s="2" t="n"/>
+      <c r="P105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -7553,15 +7623,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr"/>
-      <c r="P106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="n"/>
+      <c r="I106" s="2" t="n"/>
+      <c r="J106" s="2" t="n"/>
+      <c r="K106" s="2" t="n"/>
+      <c r="L106" s="2" t="n"/>
+      <c r="M106" s="2" t="n"/>
+      <c r="N106" s="2" t="n"/>
+      <c r="O106" s="2" t="n"/>
+      <c r="P106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -7599,15 +7669,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr"/>
-      <c r="N107" s="2" t="inlineStr"/>
-      <c r="O107" s="2" t="inlineStr"/>
-      <c r="P107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="n"/>
+      <c r="I107" s="2" t="n"/>
+      <c r="J107" s="2" t="n"/>
+      <c r="K107" s="2" t="n"/>
+      <c r="L107" s="2" t="n"/>
+      <c r="M107" s="2" t="n"/>
+      <c r="N107" s="2" t="n"/>
+      <c r="O107" s="2" t="n"/>
+      <c r="P107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7645,15 +7715,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
-      <c r="P108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="n"/>
+      <c r="I108" s="2" t="n"/>
+      <c r="J108" s="2" t="n"/>
+      <c r="K108" s="2" t="n"/>
+      <c r="L108" s="2" t="n"/>
+      <c r="M108" s="2" t="n"/>
+      <c r="N108" s="2" t="n"/>
+      <c r="O108" s="2" t="n"/>
+      <c r="P108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7691,15 +7761,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="2" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr"/>
-      <c r="O109" s="2" t="inlineStr"/>
-      <c r="P109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="n"/>
+      <c r="I109" s="2" t="n"/>
+      <c r="J109" s="2" t="n"/>
+      <c r="K109" s="2" t="n"/>
+      <c r="L109" s="2" t="n"/>
+      <c r="M109" s="2" t="n"/>
+      <c r="N109" s="2" t="n"/>
+      <c r="O109" s="2" t="n"/>
+      <c r="P109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7737,77 +7807,77 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr"/>
-      <c r="N110" s="2" t="inlineStr"/>
-      <c r="O110" s="2" t="inlineStr"/>
-      <c r="P110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2" t="n"/>
+      <c r="J110" s="2" t="n"/>
+      <c r="K110" s="2" t="n"/>
+      <c r="L110" s="2" t="n"/>
+      <c r="M110" s="2" t="n"/>
+      <c r="N110" s="2" t="n"/>
+      <c r="O110" s="2" t="n"/>
+      <c r="P110" s="2" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr"/>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="A111" s="4" t="n"/>
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>Arohera Lt3</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr"/>
-      <c r="D111" s="5" t="inlineStr"/>
-      <c r="E111" s="5" t="inlineStr"/>
-      <c r="F111" s="5" t="inlineStr">
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="n"/>
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="G111" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr">
+      <c r="H111" s="4" t="inlineStr">
         <is>
           <t>arohera-lt3</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="I111" s="4" t="inlineStr">
         <is>
           <t>10.11.32.200</t>
         </is>
       </c>
-      <c r="J111" s="5" t="inlineStr">
+      <c r="J111" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K111" s="5" t="inlineStr">
+      <c r="K111" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L111" s="5" t="inlineStr">
+      <c r="L111" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M111" s="5" t="inlineStr">
+      <c r="M111" s="4" t="inlineStr">
         <is>
           <t>samator@88</t>
         </is>
       </c>
-      <c r="N111" s="5" t="inlineStr">
+      <c r="N111" s="4" t="inlineStr">
         <is>
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O111" s="11" t="inlineStr">
+      <c r="O111" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P111" s="11" t="n">
+      <c r="P111" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7847,15 +7917,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-      <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="inlineStr"/>
-      <c r="N112" s="2" t="inlineStr"/>
-      <c r="O112" s="2" t="inlineStr"/>
-      <c r="P112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2" t="n"/>
+      <c r="J112" s="2" t="n"/>
+      <c r="K112" s="2" t="n"/>
+      <c r="L112" s="2" t="n"/>
+      <c r="M112" s="2" t="n"/>
+      <c r="N112" s="2" t="n"/>
+      <c r="O112" s="2" t="n"/>
+      <c r="P112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7893,15 +7963,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-      <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="2" t="inlineStr"/>
-      <c r="N113" s="2" t="inlineStr"/>
-      <c r="O113" s="2" t="inlineStr"/>
-      <c r="P113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="n"/>
+      <c r="I113" s="2" t="n"/>
+      <c r="J113" s="2" t="n"/>
+      <c r="K113" s="2" t="n"/>
+      <c r="L113" s="2" t="n"/>
+      <c r="M113" s="2" t="n"/>
+      <c r="N113" s="2" t="n"/>
+      <c r="O113" s="2" t="n"/>
+      <c r="P113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7939,15 +8009,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="inlineStr"/>
-      <c r="N114" s="2" t="inlineStr"/>
-      <c r="O114" s="2" t="inlineStr"/>
-      <c r="P114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="n"/>
+      <c r="I114" s="2" t="n"/>
+      <c r="J114" s="2" t="n"/>
+      <c r="K114" s="2" t="n"/>
+      <c r="L114" s="2" t="n"/>
+      <c r="M114" s="2" t="n"/>
+      <c r="N114" s="2" t="n"/>
+      <c r="O114" s="2" t="n"/>
+      <c r="P114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7985,15 +8055,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-      <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="2" t="inlineStr"/>
-      <c r="M115" s="2" t="inlineStr"/>
-      <c r="N115" s="2" t="inlineStr"/>
-      <c r="O115" s="2" t="inlineStr"/>
-      <c r="P115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="n"/>
+      <c r="I115" s="2" t="n"/>
+      <c r="J115" s="2" t="n"/>
+      <c r="K115" s="2" t="n"/>
+      <c r="L115" s="2" t="n"/>
+      <c r="M115" s="2" t="n"/>
+      <c r="N115" s="2" t="n"/>
+      <c r="O115" s="2" t="n"/>
+      <c r="P115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -8031,15 +8101,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr"/>
-      <c r="O116" s="2" t="inlineStr"/>
-      <c r="P116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="n"/>
+      <c r="I116" s="2" t="n"/>
+      <c r="J116" s="2" t="n"/>
+      <c r="K116" s="2" t="n"/>
+      <c r="L116" s="2" t="n"/>
+      <c r="M116" s="2" t="n"/>
+      <c r="N116" s="2" t="n"/>
+      <c r="O116" s="2" t="n"/>
+      <c r="P116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -8077,15 +8147,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-      <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="inlineStr"/>
-      <c r="M117" s="2" t="inlineStr"/>
-      <c r="N117" s="2" t="inlineStr"/>
-      <c r="O117" s="2" t="inlineStr"/>
-      <c r="P117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="n"/>
+      <c r="I117" s="2" t="n"/>
+      <c r="J117" s="2" t="n"/>
+      <c r="K117" s="2" t="n"/>
+      <c r="L117" s="2" t="n"/>
+      <c r="M117" s="2" t="n"/>
+      <c r="N117" s="2" t="n"/>
+      <c r="O117" s="2" t="n"/>
+      <c r="P117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -8123,15 +8193,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
-      <c r="M118" s="2" t="inlineStr"/>
-      <c r="N118" s="2" t="inlineStr"/>
-      <c r="O118" s="2" t="inlineStr"/>
-      <c r="P118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="n"/>
+      <c r="I118" s="2" t="n"/>
+      <c r="J118" s="2" t="n"/>
+      <c r="K118" s="2" t="n"/>
+      <c r="L118" s="2" t="n"/>
+      <c r="M118" s="2" t="n"/>
+      <c r="N118" s="2" t="n"/>
+      <c r="O118" s="2" t="n"/>
+      <c r="P118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -8169,15 +8239,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr"/>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-      <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="2" t="inlineStr"/>
-      <c r="M119" s="2" t="inlineStr"/>
-      <c r="N119" s="2" t="inlineStr"/>
-      <c r="O119" s="2" t="inlineStr"/>
-      <c r="P119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
+      <c r="J119" s="2" t="n"/>
+      <c r="K119" s="2" t="n"/>
+      <c r="L119" s="2" t="n"/>
+      <c r="M119" s="2" t="n"/>
+      <c r="N119" s="2" t="n"/>
+      <c r="O119" s="2" t="n"/>
+      <c r="P119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -8215,15 +8285,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="2" t="inlineStr"/>
-      <c r="N120" s="2" t="inlineStr"/>
-      <c r="O120" s="2" t="inlineStr"/>
-      <c r="P120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="n"/>
+      <c r="I120" s="2" t="n"/>
+      <c r="J120" s="2" t="n"/>
+      <c r="K120" s="2" t="n"/>
+      <c r="L120" s="2" t="n"/>
+      <c r="M120" s="2" t="n"/>
+      <c r="N120" s="2" t="n"/>
+      <c r="O120" s="2" t="n"/>
+      <c r="P120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -8261,15 +8331,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-      <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="2" t="inlineStr"/>
-      <c r="M121" s="2" t="inlineStr"/>
-      <c r="N121" s="2" t="inlineStr"/>
-      <c r="O121" s="2" t="inlineStr"/>
-      <c r="P121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="n"/>
+      <c r="I121" s="2" t="n"/>
+      <c r="J121" s="2" t="n"/>
+      <c r="K121" s="2" t="n"/>
+      <c r="L121" s="2" t="n"/>
+      <c r="M121" s="2" t="n"/>
+      <c r="N121" s="2" t="n"/>
+      <c r="O121" s="2" t="n"/>
+      <c r="P121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -8307,93 +8377,93 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr"/>
-      <c r="M122" s="2" t="inlineStr"/>
-      <c r="N122" s="2" t="inlineStr"/>
-      <c r="O122" s="2" t="inlineStr"/>
-      <c r="P122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="n"/>
+      <c r="I122" s="2" t="n"/>
+      <c r="J122" s="2" t="n"/>
+      <c r="K122" s="2" t="n"/>
+      <c r="L122" s="2" t="n"/>
+      <c r="M122" s="2" t="n"/>
+      <c r="N122" s="2" t="n"/>
+      <c r="O122" s="2" t="n"/>
+      <c r="P122" s="2" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
+      <c r="A123" s="4" t="inlineStr">
         <is>
           <t>SBM002</t>
         </is>
       </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>DEPO SINGARAJA</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>SBM</t>
         </is>
       </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="D123" s="4" t="inlineStr">
         <is>
           <t>Singaraja</t>
         </is>
       </c>
-      <c r="E123" s="5" t="inlineStr">
+      <c r="E123" s="4" t="inlineStr">
         <is>
           <t>Bali</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
+      <c r="F123" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G123" s="5" t="inlineStr">
+      <c r="G123" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H123" s="5" t="inlineStr">
+      <c r="H123" s="4" t="inlineStr">
         <is>
           <t>depo-singaraja</t>
         </is>
       </c>
-      <c r="I123" s="5" t="inlineStr">
+      <c r="I123" s="4" t="inlineStr">
         <is>
           <t>10.70.187.200</t>
         </is>
       </c>
-      <c r="J123" s="5" t="inlineStr">
+      <c r="J123" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K123" s="5" t="inlineStr">
+      <c r="K123" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L123" s="5" t="inlineStr">
+      <c r="L123" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M123" s="5" t="inlineStr">
+      <c r="M123" s="4" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="N123" s="5" t="inlineStr">
+      <c r="N123" s="4" t="inlineStr">
         <is>
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O123" s="12" t="inlineStr">
+      <c r="O123" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P123" s="12" t="n">
+      <c r="P123" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8433,269 +8503,269 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr"/>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr"/>
-      <c r="M124" s="2" t="inlineStr"/>
-      <c r="N124" s="2" t="inlineStr"/>
-      <c r="O124" s="2" t="inlineStr"/>
-      <c r="P124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="n"/>
+      <c r="I124" s="2" t="n"/>
+      <c r="J124" s="2" t="n"/>
+      <c r="K124" s="2" t="n"/>
+      <c r="L124" s="2" t="n"/>
+      <c r="M124" s="2" t="n"/>
+      <c r="N124" s="2" t="n"/>
+      <c r="O124" s="2" t="n"/>
+      <c r="P124" s="2" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr"/>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="A125" s="4" t="n"/>
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>Depo Pangkalan Bun</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr"/>
-      <c r="D125" s="5" t="inlineStr"/>
-      <c r="E125" s="5" t="inlineStr"/>
-      <c r="F125" s="5" t="inlineStr">
+      <c r="C125" s="4" t="n"/>
+      <c r="D125" s="4" t="n"/>
+      <c r="E125" s="4" t="n"/>
+      <c r="F125" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G125" s="5" t="inlineStr">
+      <c r="G125" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H125" s="5" t="inlineStr">
+      <c r="H125" s="4" t="inlineStr">
         <is>
           <t>depo-pangkalan-bun</t>
         </is>
       </c>
-      <c r="I125" s="5" t="inlineStr">
+      <c r="I125" s="4" t="inlineStr">
         <is>
           <t>10.70.224.200</t>
         </is>
       </c>
-      <c r="J125" s="5" t="inlineStr">
+      <c r="J125" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K125" s="5" t="inlineStr">
+      <c r="K125" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L125" s="5" t="inlineStr">
+      <c r="L125" s="4" t="inlineStr">
         <is>
           <t>sandana@gk</t>
         </is>
       </c>
-      <c r="M125" s="5" t="inlineStr">
+      <c r="M125" s="4" t="inlineStr">
         <is>
           <t>samator#2017</t>
         </is>
       </c>
-      <c r="N125" s="5" t="inlineStr">
+      <c r="N125" s="4" t="inlineStr">
         <is>
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O125" s="11" t="inlineStr">
+      <c r="O125" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P125" s="11" t="n">
+      <c r="P125" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr"/>
-      <c r="B126" s="5" t="inlineStr">
+      <c r="A126" s="4" t="n"/>
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>Head Office Jakarta</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr"/>
-      <c r="D126" s="5" t="inlineStr"/>
-      <c r="E126" s="5" t="inlineStr"/>
-      <c r="F126" s="5" t="inlineStr">
+      <c r="C126" s="4" t="n"/>
+      <c r="D126" s="4" t="n"/>
+      <c r="E126" s="4" t="n"/>
+      <c r="F126" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G126" s="5" t="inlineStr">
+      <c r="G126" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H126" s="5" t="inlineStr">
+      <c r="H126" s="4" t="inlineStr">
         <is>
           <t>head-office-jakarta</t>
         </is>
       </c>
-      <c r="I126" s="5" t="inlineStr">
+      <c r="I126" s="4" t="inlineStr">
         <is>
           <t>192.168.50.200</t>
         </is>
       </c>
-      <c r="J126" s="5" t="inlineStr">
+      <c r="J126" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K126" s="5" t="inlineStr">
+      <c r="K126" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L126" s="5" t="inlineStr">
+      <c r="L126" s="4" t="inlineStr">
         <is>
           <t>samator</t>
         </is>
       </c>
-      <c r="M126" s="5" t="inlineStr">
+      <c r="M126" s="4" t="inlineStr">
         <is>
           <t>samator88</t>
         </is>
       </c>
-      <c r="N126" s="5" t="inlineStr">
+      <c r="N126" s="4" t="inlineStr">
         <is>
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O126" s="11" t="inlineStr">
+      <c r="O126" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P126" s="11" t="n">
+      <c r="P126" s="5" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr"/>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="A127" s="4" t="n"/>
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>Head Office Surabaya</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr"/>
-      <c r="D127" s="5" t="inlineStr"/>
-      <c r="E127" s="5" t="inlineStr"/>
-      <c r="F127" s="5" t="inlineStr">
+      <c r="C127" s="4" t="n"/>
+      <c r="D127" s="4" t="n"/>
+      <c r="E127" s="4" t="n"/>
+      <c r="F127" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G127" s="5" t="inlineStr">
+      <c r="G127" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr">
+      <c r="H127" s="4" t="inlineStr">
         <is>
           <t>head-office-surabaya</t>
         </is>
       </c>
-      <c r="I127" s="5" t="inlineStr">
+      <c r="I127" s="4" t="inlineStr">
         <is>
           <t>172.19.19.2</t>
         </is>
       </c>
-      <c r="J127" s="5" t="inlineStr">
+      <c r="J127" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K127" s="5" t="inlineStr">
+      <c r="K127" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L127" s="5" t="inlineStr">
+      <c r="L127" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M127" s="5" t="inlineStr">
+      <c r="M127" s="4" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="N127" s="5" t="inlineStr">
+      <c r="N127" s="4" t="inlineStr">
         <is>
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O127" s="12" t="inlineStr">
+      <c r="O127" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P127" s="12" t="n">
+      <c r="P127" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr"/>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="A128" s="4" t="n"/>
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>Ho Sby Lantai 15</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr"/>
-      <c r="D128" s="5" t="inlineStr"/>
-      <c r="E128" s="5" t="inlineStr"/>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="C128" s="4" t="n"/>
+      <c r="D128" s="4" t="n"/>
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G128" s="5" t="inlineStr">
+      <c r="G128" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H128" s="5" t="inlineStr">
+      <c r="H128" s="4" t="inlineStr">
         <is>
           <t>ho-sby-lantai-15</t>
         </is>
       </c>
-      <c r="I128" s="5" t="inlineStr">
+      <c r="I128" s="4" t="inlineStr">
         <is>
           <t>10.15.18.200</t>
         </is>
       </c>
-      <c r="J128" s="5" t="inlineStr">
+      <c r="J128" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K128" s="5" t="inlineStr">
+      <c r="K128" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L128" s="5" t="inlineStr">
+      <c r="L128" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M128" s="5" t="inlineStr">
+      <c r="M128" s="4" t="inlineStr">
         <is>
           <t>Aremania87</t>
         </is>
       </c>
-      <c r="N128" s="5" t="inlineStr">
+      <c r="N128" s="4" t="inlineStr">
         <is>
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O128" s="11" t="inlineStr">
+      <c r="O128" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P128" s="11" t="n">
+      <c r="P128" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -8735,93 +8805,93 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-      <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="2" t="inlineStr"/>
-      <c r="M129" s="2" t="inlineStr"/>
-      <c r="N129" s="2" t="inlineStr"/>
-      <c r="O129" s="2" t="inlineStr"/>
-      <c r="P129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="n"/>
+      <c r="I129" s="2" t="n"/>
+      <c r="J129" s="2" t="n"/>
+      <c r="K129" s="2" t="n"/>
+      <c r="L129" s="2" t="n"/>
+      <c r="M129" s="2" t="n"/>
+      <c r="N129" s="2" t="n"/>
+      <c r="O129" s="2" t="n"/>
+      <c r="P129" s="2" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="inlineStr">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>SGI045</t>
         </is>
       </c>
-      <c r="B130" s="5" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>SGI KUDUS</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>SGI</t>
         </is>
       </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="D130" s="4" t="inlineStr">
         <is>
           <t>Kudus</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr">
+      <c r="E130" s="4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="F130" s="5" t="inlineStr">
+      <c r="F130" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G130" s="5" t="inlineStr">
+      <c r="G130" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H130" s="5" t="inlineStr">
+      <c r="H130" s="4" t="inlineStr">
         <is>
           <t>sgi-kudus</t>
         </is>
       </c>
-      <c r="I130" s="5" t="inlineStr">
+      <c r="I130" s="4" t="inlineStr">
         <is>
           <t>10.70.138.200</t>
         </is>
       </c>
-      <c r="J130" s="5" t="inlineStr">
+      <c r="J130" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K130" s="5" t="inlineStr">
+      <c r="K130" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L130" s="5" t="inlineStr">
+      <c r="L130" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M130" s="5" t="inlineStr">
+      <c r="M130" s="4" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="N130" s="5" t="inlineStr">
+      <c r="N130" s="4" t="inlineStr">
         <is>
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O130" s="11" t="inlineStr">
+      <c r="O130" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P130" s="11" t="n">
+      <c r="P130" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -8861,15 +8931,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-      <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="inlineStr"/>
-      <c r="M131" s="2" t="inlineStr"/>
-      <c r="N131" s="2" t="inlineStr"/>
-      <c r="O131" s="2" t="inlineStr"/>
-      <c r="P131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="n"/>
+      <c r="I131" s="2" t="n"/>
+      <c r="J131" s="2" t="n"/>
+      <c r="K131" s="2" t="n"/>
+      <c r="L131" s="2" t="n"/>
+      <c r="M131" s="2" t="n"/>
+      <c r="N131" s="2" t="n"/>
+      <c r="O131" s="2" t="n"/>
+      <c r="P131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -8907,15 +8977,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr"/>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-      <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="inlineStr"/>
-      <c r="M132" s="2" t="inlineStr"/>
-      <c r="N132" s="2" t="inlineStr"/>
-      <c r="O132" s="2" t="inlineStr"/>
-      <c r="P132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="n"/>
+      <c r="I132" s="2" t="n"/>
+      <c r="J132" s="2" t="n"/>
+      <c r="K132" s="2" t="n"/>
+      <c r="L132" s="2" t="n"/>
+      <c r="M132" s="2" t="n"/>
+      <c r="N132" s="2" t="n"/>
+      <c r="O132" s="2" t="n"/>
+      <c r="P132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8953,15 +9023,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-      <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="2" t="inlineStr"/>
-      <c r="M133" s="2" t="inlineStr"/>
-      <c r="N133" s="2" t="inlineStr"/>
-      <c r="O133" s="2" t="inlineStr"/>
-      <c r="P133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="n"/>
+      <c r="I133" s="2" t="n"/>
+      <c r="J133" s="2" t="n"/>
+      <c r="K133" s="2" t="n"/>
+      <c r="L133" s="2" t="n"/>
+      <c r="M133" s="2" t="n"/>
+      <c r="N133" s="2" t="n"/>
+      <c r="O133" s="2" t="n"/>
+      <c r="P133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8999,15 +9069,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-      <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="inlineStr"/>
-      <c r="N134" s="2" t="inlineStr"/>
-      <c r="O134" s="2" t="inlineStr"/>
-      <c r="P134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="n"/>
+      <c r="I134" s="2" t="n"/>
+      <c r="J134" s="2" t="n"/>
+      <c r="K134" s="2" t="n"/>
+      <c r="L134" s="2" t="n"/>
+      <c r="M134" s="2" t="n"/>
+      <c r="N134" s="2" t="n"/>
+      <c r="O134" s="2" t="n"/>
+      <c r="P134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -9045,781 +9115,781 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-      <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="2" t="inlineStr"/>
-      <c r="M135" s="2" t="inlineStr"/>
-      <c r="N135" s="2" t="inlineStr"/>
-      <c r="O135" s="2" t="inlineStr"/>
-      <c r="P135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="n"/>
+      <c r="I135" s="2" t="n"/>
+      <c r="J135" s="2" t="n"/>
+      <c r="K135" s="2" t="n"/>
+      <c r="L135" s="2" t="n"/>
+      <c r="M135" s="2" t="n"/>
+      <c r="N135" s="2" t="n"/>
+      <c r="O135" s="2" t="n"/>
+      <c r="P135" s="2" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr"/>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="A136" s="4" t="n"/>
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t>Samator Wasegas Bojonegoro</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr"/>
-      <c r="D136" s="5" t="inlineStr"/>
-      <c r="E136" s="5" t="inlineStr"/>
-      <c r="F136" s="5" t="inlineStr">
+      <c r="C136" s="4" t="n"/>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="4" t="n"/>
+      <c r="F136" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G136" s="5" t="inlineStr">
+      <c r="G136" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H136" s="5" t="inlineStr">
+      <c r="H136" s="4" t="inlineStr">
         <is>
           <t>samator-wasegas-bojonegoro</t>
         </is>
       </c>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="I136" s="4" t="inlineStr">
         <is>
           <t>10.70.175.200</t>
         </is>
       </c>
-      <c r="J136" s="5" t="inlineStr">
+      <c r="J136" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K136" s="5" t="inlineStr">
+      <c r="K136" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L136" s="5" t="inlineStr">
+      <c r="L136" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M136" s="5" t="inlineStr">
+      <c r="M136" s="4" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="N136" s="5" t="inlineStr">
+      <c r="N136" s="4" t="inlineStr">
         <is>
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O136" s="12" t="inlineStr">
+      <c r="O136" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P136" s="12" t="n">
+      <c r="P136" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="inlineStr"/>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="A137" s="4" t="n"/>
+      <c r="B137" s="4" t="inlineStr">
         <is>
           <t>Sandana Adi Prakarsa</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr"/>
-      <c r="D137" s="5" t="inlineStr"/>
-      <c r="E137" s="5" t="inlineStr"/>
-      <c r="F137" s="5" t="inlineStr">
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="4" t="n"/>
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G137" s="5" t="inlineStr">
+      <c r="G137" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H137" s="5" t="inlineStr">
+      <c r="H137" s="4" t="inlineStr">
         <is>
           <t>sandana-adi-prakarsa</t>
         </is>
       </c>
-      <c r="I137" s="5" t="inlineStr">
+      <c r="I137" s="4" t="inlineStr">
         <is>
           <t>10.100.1.200</t>
         </is>
       </c>
-      <c r="J137" s="5" t="inlineStr">
+      <c r="J137" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K137" s="5" t="inlineStr">
+      <c r="K137" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L137" s="5" t="inlineStr">
+      <c r="L137" s="4" t="inlineStr">
         <is>
           <t>sandana_AP</t>
         </is>
       </c>
-      <c r="M137" s="5" t="inlineStr">
+      <c r="M137" s="4" t="inlineStr">
         <is>
           <t>samator#2017</t>
         </is>
       </c>
-      <c r="N137" s="5" t="inlineStr">
+      <c r="N137" s="4" t="inlineStr">
         <is>
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O137" s="11" t="inlineStr">
+      <c r="O137" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P137" s="11" t="n">
+      <c r="P137" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="inlineStr"/>
-      <c r="B138" s="5" t="inlineStr">
+      <c r="A138" s="4" t="n"/>
+      <c r="B138" s="4" t="inlineStr">
         <is>
           <t>Sandana Baswara Gas</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr"/>
-      <c r="D138" s="5" t="inlineStr"/>
-      <c r="E138" s="5" t="inlineStr"/>
-      <c r="F138" s="5" t="inlineStr">
+      <c r="C138" s="4" t="n"/>
+      <c r="D138" s="4" t="n"/>
+      <c r="E138" s="4" t="n"/>
+      <c r="F138" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G138" s="5" t="inlineStr">
+      <c r="G138" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H138" s="5" t="inlineStr">
+      <c r="H138" s="4" t="inlineStr">
         <is>
           <t>sandana-baswara-gas</t>
         </is>
       </c>
-      <c r="I138" s="5" t="inlineStr">
+      <c r="I138" s="4" t="inlineStr">
         <is>
           <t>10.70.207.200</t>
         </is>
       </c>
-      <c r="J138" s="5" t="inlineStr">
+      <c r="J138" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K138" s="5" t="inlineStr">
+      <c r="K138" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L138" s="5" t="inlineStr">
+      <c r="L138" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M138" s="5" t="inlineStr">
+      <c r="M138" s="4" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="N138" s="5" t="inlineStr">
+      <c r="N138" s="4" t="inlineStr">
         <is>
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O138" s="11" t="inlineStr">
+      <c r="O138" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P138" s="11" t="n">
+      <c r="P138" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr"/>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="A139" s="4" t="n"/>
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>Satoe</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr"/>
-      <c r="D139" s="5" t="inlineStr"/>
-      <c r="E139" s="5" t="inlineStr"/>
-      <c r="F139" s="5" t="inlineStr">
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="4" t="n"/>
+      <c r="E139" s="4" t="n"/>
+      <c r="F139" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G139" s="5" t="inlineStr">
+      <c r="G139" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H139" s="5" t="inlineStr">
+      <c r="H139" s="4" t="inlineStr">
         <is>
           <t>satoe</t>
         </is>
       </c>
-      <c r="I139" s="5" t="inlineStr">
+      <c r="I139" s="4" t="inlineStr">
         <is>
           <t>10.70.181.110</t>
         </is>
       </c>
-      <c r="J139" s="5" t="inlineStr">
+      <c r="J139" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K139" s="5" t="inlineStr">
+      <c r="K139" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L139" s="5" t="inlineStr">
+      <c r="L139" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M139" s="5" t="inlineStr">
+      <c r="M139" s="4" t="inlineStr">
         <is>
           <t>abcd1234</t>
         </is>
       </c>
-      <c r="N139" s="5" t="inlineStr">
+      <c r="N139" s="4" t="inlineStr">
         <is>
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O139" s="11" t="inlineStr">
+      <c r="O139" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P139" s="11" t="n">
+      <c r="P139" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr"/>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="A140" s="4" t="n"/>
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>Sgi Batam 2</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr"/>
-      <c r="D140" s="5" t="inlineStr"/>
-      <c r="E140" s="5" t="inlineStr"/>
-      <c r="F140" s="5" t="inlineStr">
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4" t="n"/>
+      <c r="E140" s="4" t="n"/>
+      <c r="F140" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G140" s="5" t="inlineStr">
+      <c r="G140" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H140" s="5" t="inlineStr">
+      <c r="H140" s="4" t="inlineStr">
         <is>
           <t>sgi-batam-2</t>
         </is>
       </c>
-      <c r="I140" s="5" t="inlineStr">
+      <c r="I140" s="4" t="inlineStr">
         <is>
           <t>192.168.70.119</t>
         </is>
       </c>
-      <c r="J140" s="5" t="inlineStr">
+      <c r="J140" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K140" s="5" t="inlineStr">
+      <c r="K140" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L140" s="5" t="inlineStr">
+      <c r="L140" s="4" t="inlineStr">
         <is>
           <t>sgibatam</t>
         </is>
       </c>
-      <c r="M140" s="5" t="inlineStr">
+      <c r="M140" s="4" t="inlineStr">
         <is>
           <t>samator#2017</t>
         </is>
       </c>
-      <c r="N140" s="5" t="inlineStr">
+      <c r="N140" s="4" t="inlineStr">
         <is>
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O140" s="11" t="inlineStr">
+      <c r="O140" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P140" s="11" t="n">
+      <c r="P140" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="inlineStr"/>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="A141" s="4" t="n"/>
+      <c r="B141" s="4" t="inlineStr">
         <is>
           <t>Sgi Kaligawe</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr"/>
-      <c r="D141" s="5" t="inlineStr"/>
-      <c r="E141" s="5" t="inlineStr"/>
-      <c r="F141" s="5" t="inlineStr">
+      <c r="C141" s="4" t="n"/>
+      <c r="D141" s="4" t="n"/>
+      <c r="E141" s="4" t="n"/>
+      <c r="F141" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G141" s="5" t="inlineStr">
+      <c r="G141" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H141" s="5" t="inlineStr">
+      <c r="H141" s="4" t="inlineStr">
         <is>
           <t>sgi-kaligawe</t>
         </is>
       </c>
-      <c r="I141" s="5" t="inlineStr">
+      <c r="I141" s="4" t="inlineStr">
         <is>
           <t>10.70.123.200</t>
         </is>
       </c>
-      <c r="J141" s="5" t="inlineStr">
+      <c r="J141" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K141" s="5" t="inlineStr">
+      <c r="K141" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L141" s="5" t="inlineStr">
+      <c r="L141" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M141" s="5" t="inlineStr">
+      <c r="M141" s="4" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="N141" s="5" t="inlineStr">
+      <c r="N141" s="4" t="inlineStr">
         <is>
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O141" s="13" t="inlineStr">
+      <c r="O141" s="7" t="inlineStr">
         <is>
           <t>auth_error</t>
         </is>
       </c>
-      <c r="P141" s="13" t="n">
+      <c r="P141" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="inlineStr"/>
-      <c r="B142" s="5" t="inlineStr">
+      <c r="A142" s="4" t="n"/>
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>Sgi Lubuk Gaung Dumai</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr"/>
-      <c r="D142" s="5" t="inlineStr"/>
-      <c r="E142" s="5" t="inlineStr"/>
-      <c r="F142" s="5" t="inlineStr">
+      <c r="C142" s="4" t="n"/>
+      <c r="D142" s="4" t="n"/>
+      <c r="E142" s="4" t="n"/>
+      <c r="F142" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G142" s="5" t="inlineStr">
+      <c r="G142" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H142" s="5" t="inlineStr">
+      <c r="H142" s="4" t="inlineStr">
         <is>
           <t>sgi-lubuk-gaung-dumai</t>
         </is>
       </c>
-      <c r="I142" s="5" t="inlineStr">
+      <c r="I142" s="4" t="inlineStr">
         <is>
           <t>192.168.94.200</t>
         </is>
       </c>
-      <c r="J142" s="5" t="inlineStr">
+      <c r="J142" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K142" s="5" t="inlineStr">
+      <c r="K142" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L142" s="5" t="inlineStr">
+      <c r="L142" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M142" s="5" t="inlineStr">
+      <c r="M142" s="4" t="inlineStr">
         <is>
           <t>Samator01</t>
         </is>
       </c>
-      <c r="N142" s="5" t="inlineStr">
+      <c r="N142" s="4" t="inlineStr">
         <is>
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O142" s="11" t="inlineStr">
+      <c r="O142" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P142" s="11" t="n">
+      <c r="P142" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr"/>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="A143" s="4" t="n"/>
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>Sgi Pier</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr"/>
-      <c r="D143" s="5" t="inlineStr"/>
-      <c r="E143" s="5" t="inlineStr"/>
-      <c r="F143" s="5" t="inlineStr">
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="n"/>
+      <c r="E143" s="4" t="n"/>
+      <c r="F143" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G143" s="5" t="inlineStr">
+      <c r="G143" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H143" s="5" t="inlineStr">
+      <c r="H143" s="4" t="inlineStr">
         <is>
           <t>sgi-pier</t>
         </is>
       </c>
-      <c r="I143" s="5" t="inlineStr">
+      <c r="I143" s="4" t="inlineStr">
         <is>
           <t>192.168.15.200</t>
         </is>
       </c>
-      <c r="J143" s="5" t="inlineStr">
+      <c r="J143" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K143" s="5" t="inlineStr">
+      <c r="K143" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L143" s="5" t="inlineStr">
+      <c r="L143" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M143" s="5" t="inlineStr">
+      <c r="M143" s="4" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="N143" s="5" t="inlineStr">
+      <c r="N143" s="4" t="inlineStr">
         <is>
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O143" s="11" t="inlineStr">
+      <c r="O143" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P143" s="11" t="n">
+      <c r="P143" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="inlineStr"/>
-      <c r="B144" s="5" t="inlineStr">
+      <c r="A144" s="4" t="n"/>
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>Sig Kendal 1</t>
         </is>
       </c>
-      <c r="C144" s="5" t="inlineStr"/>
-      <c r="D144" s="5" t="inlineStr"/>
-      <c r="E144" s="5" t="inlineStr"/>
-      <c r="F144" s="5" t="inlineStr">
+      <c r="C144" s="4" t="n"/>
+      <c r="D144" s="4" t="n"/>
+      <c r="E144" s="4" t="n"/>
+      <c r="F144" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G144" s="5" t="inlineStr">
+      <c r="G144" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H144" s="5" t="inlineStr">
+      <c r="H144" s="4" t="inlineStr">
         <is>
           <t>sig-kendal-1</t>
         </is>
       </c>
-      <c r="I144" s="5" t="inlineStr">
+      <c r="I144" s="4" t="inlineStr">
         <is>
           <t>192.168.2.100</t>
         </is>
       </c>
-      <c r="J144" s="5" t="inlineStr">
+      <c r="J144" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K144" s="5" t="inlineStr">
+      <c r="K144" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L144" s="5" t="inlineStr">
+      <c r="L144" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M144" s="5" t="inlineStr">
+      <c r="M144" s="4" t="inlineStr">
         <is>
           <t>Indogas*19#</t>
         </is>
       </c>
-      <c r="N144" s="5" t="inlineStr">
+      <c r="N144" s="4" t="inlineStr">
         <is>
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O144" s="11" t="inlineStr">
+      <c r="O144" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P144" s="11" t="n">
+      <c r="P144" s="5" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr"/>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="A145" s="4" t="n"/>
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>Sig Rungkut Sier</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr"/>
-      <c r="D145" s="5" t="inlineStr"/>
-      <c r="E145" s="5" t="inlineStr"/>
-      <c r="F145" s="5" t="inlineStr">
+      <c r="C145" s="4" t="n"/>
+      <c r="D145" s="4" t="n"/>
+      <c r="E145" s="4" t="n"/>
+      <c r="F145" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G145" s="5" t="inlineStr">
+      <c r="G145" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H145" s="5" t="inlineStr">
+      <c r="H145" s="4" t="inlineStr">
         <is>
           <t>sig-rungkut-sier</t>
         </is>
       </c>
-      <c r="I145" s="5" t="inlineStr">
+      <c r="I145" s="4" t="inlineStr">
         <is>
           <t>10.70.90.200</t>
         </is>
       </c>
-      <c r="J145" s="5" t="inlineStr">
+      <c r="J145" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K145" s="5" t="inlineStr">
+      <c r="K145" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L145" s="5" t="inlineStr">
+      <c r="L145" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M145" s="5" t="inlineStr">
+      <c r="M145" s="4" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="N145" s="5" t="inlineStr">
+      <c r="N145" s="4" t="inlineStr">
         <is>
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O145" s="11" t="inlineStr">
+      <c r="O145" s="5" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="P145" s="11" t="n">
+      <c r="P145" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="inlineStr"/>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="A146" s="4" t="n"/>
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>SGI Kediri</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr"/>
-      <c r="D146" s="5" t="inlineStr"/>
-      <c r="E146" s="5" t="inlineStr"/>
-      <c r="F146" s="5" t="inlineStr">
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="n"/>
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G146" s="5" t="inlineStr">
+      <c r="G146" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H146" s="5" t="inlineStr">
+      <c r="H146" s="4" t="inlineStr">
         <is>
           <t>sgi-kediri</t>
         </is>
       </c>
-      <c r="I146" s="5" t="inlineStr">
+      <c r="I146" s="4" t="inlineStr">
         <is>
           <t>10.70.137.201</t>
         </is>
       </c>
-      <c r="J146" s="5" t="inlineStr">
+      <c r="J146" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K146" s="5" t="inlineStr">
+      <c r="K146" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L146" s="5" t="inlineStr">
+      <c r="L146" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M146" s="5" t="inlineStr">
+      <c r="M146" s="4" t="inlineStr">
         <is>
           <t>Aremania87</t>
         </is>
       </c>
-      <c r="N146" s="5" t="inlineStr">
+      <c r="N146" s="4" t="inlineStr">
         <is>
           <t>hikvision</t>
         </is>
       </c>
-      <c r="O146" s="12" t="inlineStr">
+      <c r="O146" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P146" s="12" t="n">
+      <c r="P146" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="inlineStr"/>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="A147" s="4" t="n"/>
+      <c r="B147" s="4" t="inlineStr">
         <is>
           <t>Smu Sidoarjo Sgi</t>
         </is>
       </c>
-      <c r="C147" s="5" t="inlineStr"/>
-      <c r="D147" s="5" t="inlineStr"/>
-      <c r="E147" s="5" t="inlineStr"/>
-      <c r="F147" s="5" t="inlineStr">
+      <c r="C147" s="4" t="n"/>
+      <c r="D147" s="4" t="n"/>
+      <c r="E147" s="4" t="n"/>
+      <c r="F147" s="4" t="inlineStr">
         <is>
           <t>Not in SHE Request</t>
         </is>
       </c>
-      <c r="G147" s="5" t="inlineStr">
+      <c r="G147" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H147" s="5" t="inlineStr">
+      <c r="H147" s="4" t="inlineStr">
         <is>
           <t>smu-sidoarjo-sgi</t>
         </is>
       </c>
-      <c r="I147" s="5" t="inlineStr">
+      <c r="I147" s="4" t="inlineStr">
         <is>
           <t>10.70.140.200</t>
         </is>
       </c>
-      <c r="J147" s="5" t="inlineStr">
+      <c r="J147" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K147" s="5" t="inlineStr">
+      <c r="K147" s="4" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="L147" s="5" t="inlineStr">
+      <c r="L147" s="4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="M147" s="5" t="inlineStr">
+      <c r="M147" s="4" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="N147" s="5" t="inlineStr">
+      <c r="N147" s="4" t="inlineStr">
         <is>
           <t>acti_snvr</t>
         </is>
       </c>
-      <c r="O147" s="12" t="inlineStr">
+      <c r="O147" s="6" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="P147" s="12" t="n">
+      <c r="P147" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9836,259 +9906,259 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" style="35" min="1" max="1"/>
+    <col width="72" customWidth="1" style="35" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+    <row r="1" ht="16" customHeight="1" s="35">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ROW COLOR</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>MEANING</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Pink / Light Red</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Requested by SHE — site is in the SHE access request list</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Active &amp; synced — NVR is reachable and confirmed in DB</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Yellow / Amber</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Not in SHE request — site is in DB but was not requested by SHE</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+    <row r="6" ht="16" customHeight="1" s="35">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>SYNC STATUS</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>MEANING</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>synced</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>NVR is reachable and device info has been retrieved successfully</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>unreachable</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>NVR did not respond within timeout — network/VPN issue or device offline</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>auth_error</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>NVR responded but login failed — credentials need to be updated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>NVR responded but ISAPI returned an error — possibly wrong vendor type</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Not yet probed since last import</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="13" ht="16" customHeight="1" s="35">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>COLUMN</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>MEANING</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Plant Code</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Epicor plant code (e.g. SGI046)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Site Name</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Official site name used in SHE/Epicor</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Legal entity (SGI, SIG, AME, SMT, etc.)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>SHE Status</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Whether SHE has requested CCTV access for this site</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>In DB</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>YES = NVR is registered in the CCTV system database</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>DB Code</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Unique identifier used in the CCTV system (slug format)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>NVR IP</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>IP address of the NVR on the internal network</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>NVR brand/protocol: hikvision | acti_snvr | uniview | hilook</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Sync Status</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Result of last probe (see Sync Status table above)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Channels</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Number of camera channels discovered on this NVR</t>
         </is>
@@ -10106,1351 +10176,1351 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" style="35" min="1" max="1"/>
+    <col width="30" customWidth="1" style="35" min="2" max="2"/>
+    <col width="14" customWidth="1" style="35" min="3" max="3"/>
+    <col width="24" customWidth="1" style="35" min="4" max="4"/>
+    <col width="48" customWidth="1" style="35" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="35">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Playback Test Results — 2026-06-23, Channel 1, 10:00–10:01 WIB</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="35">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>52 NVRs tested  |  24 Works  |  26 No Recording  |  2 API Not Supported</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+    <row r="3" ht="20" customHeight="1" s="35">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Site Code</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Playback Status</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="24" t="n">
+    <row r="4" ht="16" customHeight="1" s="35">
+      <c r="A4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>arohera-lt3</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="27" t="n">
+    <row r="5" ht="16" customHeight="1" s="35">
+      <c r="A5" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>depo-pangkalan-bun</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="24" t="n">
+    <row r="6" ht="16" customHeight="1" s="35">
+      <c r="A6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>depo-purwodadi</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="27" t="n">
+    <row r="7" ht="16" customHeight="1" s="35">
+      <c r="A7" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>depo-rembang</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="24" t="n">
+    <row r="8" ht="16" customHeight="1" s="35">
+      <c r="A8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>ho-sby-lantai-15</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="27" t="n">
+    <row r="9" ht="16" customHeight="1" s="35">
+      <c r="A9" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>satoe</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="24" t="n">
+    <row r="10" ht="16" customHeight="1" s="35">
+      <c r="A10" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>sgi-bandung</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="27" t="n">
+    <row r="11" ht="16" customHeight="1" s="35">
+      <c r="A11" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>sgi-batam</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E11" s="29" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="24" t="n">
+    <row r="12" ht="16" customHeight="1" s="35">
+      <c r="A12" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>sgi-batam-2</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="27" t="n">
+    <row r="13" ht="16" customHeight="1" s="35">
+      <c r="A13" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>sgi-cikande</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="24" t="n">
+    <row r="14" ht="16" customHeight="1" s="35">
+      <c r="A14" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>sgi-cikupa</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="27" t="n">
+    <row r="15" ht="16" customHeight="1" s="35">
+      <c r="A15" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>sgi-lubuk-gaung-dumai</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E15" s="29" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
+    <row r="16" ht="16" customHeight="1" s="35">
+      <c r="A16" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>sgi-rantau-prapat</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="27" t="n">
+    <row r="17" ht="16" customHeight="1" s="35">
+      <c r="A17" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>sgi-tebing-tinggi</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D17" s="28" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="24" t="n">
+    <row r="18" ht="16" customHeight="1" s="35">
+      <c r="A18" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>sig-baturaja</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="27" t="n">
+    <row r="19" ht="16" customHeight="1" s="35">
+      <c r="A19" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>sig-kendal</t>
         </is>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D19" s="28" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
+    <row r="20" ht="16" customHeight="1" s="35">
+      <c r="A20" s="16" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>sig-kendal-1</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="27" t="n">
+    <row r="21" ht="16" customHeight="1" s="35">
+      <c r="A21" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>sig-lampung-3</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="24" t="n">
+    <row r="22" ht="16" customHeight="1" s="35">
+      <c r="A22" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>sig-lampung-ultimate</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="27" t="n">
+    <row r="23" ht="16" customHeight="1" s="35">
+      <c r="A23" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>sig-medan</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E23" s="29" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="24" t="n">
+    <row r="24" ht="16" customHeight="1" s="35">
+      <c r="A24" s="16" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>sig-medan-plant</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="27" t="n">
+    <row r="25" ht="16" customHeight="1" s="35">
+      <c r="A25" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>sig-pulogadung</t>
         </is>
       </c>
-      <c r="C25" s="28" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>Hilook</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E25" s="29" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="24" t="n">
+    <row r="26" ht="16" customHeight="1" s="35">
+      <c r="A26" s="16" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>sig-subang-pabrikan-pos</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="27" t="n">
+    <row r="27" ht="16" customHeight="1" s="35">
+      <c r="A27" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="28" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>smt-cilamaya</t>
         </is>
       </c>
-      <c r="C27" s="28" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>✅ Works</t>
         </is>
       </c>
-      <c r="E27" s="29" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>1 segment found</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="30" t="n">
+    <row r="28" ht="16" customHeight="1" s="35">
+      <c r="A28" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="31" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>sgi-cilegon</t>
         </is>
       </c>
-      <c r="C28" s="31" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D28" s="31" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E28" s="32" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>NVR reachable, no footage at this time</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="33" t="n">
+    <row r="29" ht="16" customHeight="1" s="35">
+      <c r="A29" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>sgi-daanmogot</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D29" s="34" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E29" s="35" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>NVR reachable, no footage at this time</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="30" t="n">
+    <row r="30" ht="16" customHeight="1" s="35">
+      <c r="A30" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="31" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>sig-bekasi-cibitung</t>
         </is>
       </c>
-      <c r="C30" s="31" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>Hikvision</t>
         </is>
       </c>
-      <c r="D30" s="31" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E30" s="32" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>NVR reachable, no footage at this time</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="33" t="n">
+    <row r="31" ht="16" customHeight="1" s="35">
+      <c r="A31" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="34" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>head-office-jakarta</t>
         </is>
       </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D31" s="34" t="inlineStr">
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E31" s="35" t="inlineStr">
+      <c r="E31" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="30" t="n">
+    <row r="32" ht="16" customHeight="1" s="35">
+      <c r="A32" s="22" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="31" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>sandana-adi-prakarsa</t>
         </is>
       </c>
-      <c r="C32" s="31" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D32" s="31" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E32" s="32" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="33" t="n">
+    <row r="33" ht="16" customHeight="1" s="35">
+      <c r="A33" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="34" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>sandana-baswara-gas</t>
         </is>
       </c>
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D33" s="34" t="inlineStr">
+      <c r="D33" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E33" s="35" t="inlineStr">
+      <c r="E33" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="30" t="n">
+    <row r="34" ht="16" customHeight="1" s="35">
+      <c r="A34" s="22" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="31" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>sgi-batakan</t>
         </is>
       </c>
-      <c r="C34" s="31" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D34" s="31" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E34" s="32" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="33" t="n">
+    <row r="35" ht="16" customHeight="1" s="35">
+      <c r="A35" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>sgi-boyolali</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D35" s="34" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E35" s="35" t="inlineStr">
+      <c r="E35" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="30" t="n">
+    <row r="36" ht="16" customHeight="1" s="35">
+      <c r="A36" s="22" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="31" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>sgi-duri</t>
         </is>
       </c>
-      <c r="C36" s="31" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D36" s="31" t="inlineStr">
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E36" s="32" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="33" t="n">
+    <row r="37" ht="16" customHeight="1" s="35">
+      <c r="A37" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="34" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>sgi-jambi</t>
         </is>
       </c>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D37" s="34" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E37" s="35" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="30" t="n">
+    <row r="38" ht="16" customHeight="1" s="35">
+      <c r="A38" s="22" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="31" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>sgi-klaten</t>
         </is>
       </c>
-      <c r="C38" s="31" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D38" s="31" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E38" s="32" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="33" t="n">
+    <row r="39" ht="16" customHeight="1" s="35">
+      <c r="A39" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>sgi-kudus</t>
         </is>
       </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D39" s="34" t="inlineStr">
+      <c r="D39" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E39" s="35" t="inlineStr">
+      <c r="E39" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="30" t="n">
+    <row r="40" ht="16" customHeight="1" s="35">
+      <c r="A40" s="22" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="31" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>sgi-kutai</t>
         </is>
       </c>
-      <c r="C40" s="31" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D40" s="31" t="inlineStr">
+      <c r="D40" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E40" s="32" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="33" t="n">
+    <row r="41" ht="16" customHeight="1" s="35">
+      <c r="A41" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="34" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>sgi-madiun</t>
         </is>
       </c>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D41" s="34" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E41" s="35" t="inlineStr">
+      <c r="E41" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="30" t="n">
+    <row r="42" ht="16" customHeight="1" s="35">
+      <c r="A42" s="22" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="31" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>sgi-magelang</t>
         </is>
       </c>
-      <c r="C42" s="31" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D42" s="31" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E42" s="32" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="33" t="n">
+    <row r="43" ht="16" customHeight="1" s="35">
+      <c r="A43" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="34" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>sgi-malang</t>
         </is>
       </c>
-      <c r="C43" s="34" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D43" s="34" t="inlineStr">
+      <c r="D43" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E43" s="35" t="inlineStr">
+      <c r="E43" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="30" t="n">
+    <row r="44" ht="16" customHeight="1" s="35">
+      <c r="A44" s="22" t="n">
         <v>41</v>
       </c>
-      <c r="B44" s="31" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>sgi-pier</t>
         </is>
       </c>
-      <c r="C44" s="31" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D44" s="31" t="inlineStr">
+      <c r="D44" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E44" s="32" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="33" t="n">
+    <row r="45" ht="16" customHeight="1" s="35">
+      <c r="A45" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="34" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>sgi-sibolga</t>
         </is>
       </c>
-      <c r="C45" s="34" t="inlineStr">
+      <c r="C45" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D45" s="34" t="inlineStr">
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E45" s="35" t="inlineStr">
+      <c r="E45" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="30" t="n">
+    <row r="46" ht="16" customHeight="1" s="35">
+      <c r="A46" s="22" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="31" t="inlineStr">
+      <c r="B46" s="23" t="inlineStr">
         <is>
           <t>sgi-tuban</t>
         </is>
       </c>
-      <c r="C46" s="31" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D46" s="31" t="inlineStr">
+      <c r="D46" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E46" s="32" t="inlineStr">
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="33" t="n">
+    <row r="47" ht="16" customHeight="1" s="35">
+      <c r="A47" s="25" t="n">
         <v>44</v>
       </c>
-      <c r="B47" s="34" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>sig-bandung</t>
         </is>
       </c>
-      <c r="C47" s="34" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D47" s="34" t="inlineStr">
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E47" s="35" t="inlineStr">
+      <c r="E47" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="30" t="n">
+    <row r="48" ht="16" customHeight="1" s="35">
+      <c r="A48" s="22" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="31" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>sig-gorontalo</t>
         </is>
       </c>
-      <c r="C48" s="31" t="inlineStr">
+      <c r="C48" s="23" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D48" s="31" t="inlineStr">
+      <c r="D48" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E48" s="32" t="inlineStr">
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="33" t="n">
+    <row r="49" ht="16" customHeight="1" s="35">
+      <c r="A49" s="25" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="34" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>sig-manado</t>
         </is>
       </c>
-      <c r="C49" s="34" t="inlineStr">
+      <c r="C49" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D49" s="34" t="inlineStr">
+      <c r="D49" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E49" s="35" t="inlineStr">
+      <c r="E49" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="30" t="n">
+    <row r="50" ht="16" customHeight="1" s="35">
+      <c r="A50" s="22" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="31" t="inlineStr">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>sig-pekanbaru</t>
         </is>
       </c>
-      <c r="C50" s="31" t="inlineStr">
+      <c r="C50" s="23" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D50" s="31" t="inlineStr">
+      <c r="D50" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E50" s="32" t="inlineStr">
+      <c r="E50" s="24" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="33" t="n">
+    <row r="51" ht="16" customHeight="1" s="35">
+      <c r="A51" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="34" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>sig-rungkut-sier</t>
         </is>
       </c>
-      <c r="C51" s="34" t="inlineStr">
+      <c r="C51" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D51" s="34" t="inlineStr">
+      <c r="D51" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E51" s="35" t="inlineStr">
+      <c r="E51" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="30" t="n">
+    <row r="52" ht="16" customHeight="1" s="35">
+      <c r="A52" s="22" t="n">
         <v>49</v>
       </c>
-      <c r="B52" s="31" t="inlineStr">
+      <c r="B52" s="23" t="inlineStr">
         <is>
           <t>sig-siantar</t>
         </is>
       </c>
-      <c r="C52" s="31" t="inlineStr">
+      <c r="C52" s="23" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D52" s="31" t="inlineStr">
+      <c r="D52" s="23" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E52" s="32" t="inlineStr">
+      <c r="E52" s="24" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="33" t="n">
+    <row r="53" ht="16" customHeight="1" s="35">
+      <c r="A53" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="B53" s="34" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>sig-ternate</t>
         </is>
       </c>
-      <c r="C53" s="34" t="inlineStr">
+      <c r="C53" s="26" t="inlineStr">
         <is>
           <t>ACTi SNVR</t>
         </is>
       </c>
-      <c r="D53" s="34" t="inlineStr">
+      <c r="D53" s="26" t="inlineStr">
         <is>
           <t>⚠️ No Recording Found</t>
         </is>
       </c>
-      <c r="E53" s="35" t="inlineStr">
+      <c r="E53" s="27" t="inlineStr">
         <is>
           <t>ACTi search API works, no footage returned</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="36" t="n">
+    <row r="54" ht="32" customHeight="1" s="35">
+      <c r="A54" s="28" t="n">
         <v>51</v>
       </c>
-      <c r="B54" s="37" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>ame-gudang-krian</t>
         </is>
       </c>
-      <c r="C54" s="37" t="inlineStr">
+      <c r="C54" s="29" t="inlineStr">
         <is>
           <t>Uniview</t>
         </is>
       </c>
-      <c r="D54" s="37" t="inlineStr">
+      <c r="D54" s="29" t="inlineStr">
         <is>
           <t>❌ API Not Supported</t>
         </is>
       </c>
-      <c r="E54" s="38" t="inlineStr">
+      <c r="E54" s="30" t="inlineStr">
         <is>
           <t>Missing /ISAPI/ContentMgmt/search — needs Uniview playback impl</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="39" t="n">
+    <row r="55" ht="32" customHeight="1" s="35">
+      <c r="A55" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="B55" s="40" t="inlineStr">
+      <c r="B55" s="32" t="inlineStr">
         <is>
           <t>sgi-bangka</t>
         </is>
       </c>
-      <c r="C55" s="40" t="inlineStr">
+      <c r="C55" s="32" t="inlineStr">
         <is>
           <t>Uniview</t>
         </is>
       </c>
-      <c r="D55" s="40" t="inlineStr">
+      <c r="D55" s="32" t="inlineStr">
         <is>
           <t>❌ API Not Supported</t>
         </is>
       </c>
-      <c r="E55" s="41" t="inlineStr">
+      <c r="E55" s="33" t="inlineStr">
         <is>
           <t>Missing /ISAPI/ContentMgmt/search — needs Uniview playback impl</t>
         </is>
